--- a/nr-keep-only-ep/ig/PN13-FHIR-prescmed-medicationnoncompound-conceptmap.xlsx
+++ b/nr-keep-only-ep/ig/PN13-FHIR-prescmed-medicationnoncompound-conceptmap.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T17:06:42+00:00</t>
+    <t>2025-11-04T08:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-keep-only-ep/ig/PN13-FHIR-prescmed-medicationnoncompound-conceptmap.xlsx
+++ b/nr-keep-only-ep/ig/PN13-FHIR-prescmed-medicationnoncompound-conceptmap.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-04T08:50:53+00:00</t>
+    <t>2025-11-04T08:57:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
